--- a/deg-concentration-calculator.xlsx
+++ b/deg-concentration-calculator.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Лист1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1037,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1138,6 +1138,17 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Контроль исходной таблицы</t>
+        </is>
+      </c>
+      <c r="B13" s="11">
+        <f>IF(AND(COUNT('Лист1'!$B$1:$B$10)=10,SUMPRODUCT(('Лист1'!$B$1:$B$9&lt;='Лист1'!$B$2:$B$10)*1)=0),"таблица в порядке: 10 точек, плотность убывает","ВНИМАНИЕ: таблица на листе «Лист1» изменена — проверьте A1:B10")</f>
+        <v/>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -1257,7 +1268,7 @@
         </is>
       </c>
       <c r="B26" s="21">
-        <f>IF(AND(ISNUMBER($B$6),$B$6&gt;=MIN('Лист1'!$B$1:$B$10),$B$6&lt;=MAX('Лист1'!$B$1:$B$10)),MIN(9,MAX(1,COUNTIF('Лист1'!$B$1:$B$10,"&gt;="&amp;$B$6))),"")</f>
+        <f>IF(AND(ISNUMBER($B$6),$B$6&gt;=MIN('Лист1'!$B$1:$B$10),$B$6&lt;=MAX('Лист1'!$B$1:$B$10)),MIN(9,MAX(1,SUMPRODUCT(('Лист1'!$B$1:$B$10&gt;=$B$6)*1))),"")</f>
         <v/>
       </c>
     </row>
@@ -1300,6 +1311,20 @@
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>5. Исходную таблицу на листе «Лист1» (A1:B10) можно дополнять/править — расчёт использует её напрямую; значения плотности должны оставаться в порядке убывания.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>6. Вводить плотность только в ячейку B6 ЭТОГО листа («Расчёт»). Не вводите её на листе «Лист1»: там в ячейках B1:B10 лежит сама зависимость, и ввод поверх них испортит таблицу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>7. Если результат не меняется при вводе новой плотности — в Excel включён ручной пересчёт: «Формулы» → «Параметры вычислений» → «Автоматически» (или нажмите F9).</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1477,7 @@
         <v/>
       </c>
       <c r="H8" s="22">
-        <f>MIN(9,MAX(1,COUNTIF($B$1:$B$10,"&gt;="&amp;D8)))</f>
+        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D8)*1)))</f>
         <v/>
       </c>
     </row>
@@ -1480,7 +1505,7 @@
         <v/>
       </c>
       <c r="H9" s="22">
-        <f>MIN(9,MAX(1,COUNTIF($B$1:$B$10,"&gt;="&amp;D9)))</f>
+        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D9)*1)))</f>
         <v/>
       </c>
     </row>
@@ -1508,7 +1533,7 @@
         <v/>
       </c>
       <c r="H10" s="22">
-        <f>MIN(9,MAX(1,COUNTIF($B$1:$B$10,"&gt;="&amp;D10)))</f>
+        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D10)*1)))</f>
         <v/>
       </c>
     </row>
@@ -1530,7 +1555,7 @@
         <v/>
       </c>
       <c r="H11" s="22">
-        <f>MIN(9,MAX(1,COUNTIF($B$1:$B$10,"&gt;="&amp;D11)))</f>
+        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D11)*1)))</f>
         <v/>
       </c>
     </row>
@@ -1552,7 +1577,7 @@
         <v/>
       </c>
       <c r="H12" s="22">
-        <f>MIN(9,MAX(1,COUNTIF($B$1:$B$10,"&gt;="&amp;D12)))</f>
+        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D12)*1)))</f>
         <v/>
       </c>
     </row>
@@ -1574,7 +1599,7 @@
         <v/>
       </c>
       <c r="H13" s="22">
-        <f>MIN(9,MAX(1,COUNTIF($B$1:$B$10,"&gt;="&amp;D13)))</f>
+        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D13)*1)))</f>
         <v/>
       </c>
     </row>
@@ -1596,7 +1621,7 @@
         <v/>
       </c>
       <c r="H14" s="22">
-        <f>MIN(9,MAX(1,COUNTIF($B$1:$B$10,"&gt;="&amp;D14)))</f>
+        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D14)*1)))</f>
         <v/>
       </c>
     </row>
@@ -1618,7 +1643,7 @@
         <v/>
       </c>
       <c r="H15" s="22">
-        <f>MIN(9,MAX(1,COUNTIF($B$1:$B$10,"&gt;="&amp;D15)))</f>
+        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D15)*1)))</f>
         <v/>
       </c>
     </row>
@@ -1640,7 +1665,7 @@
         <v/>
       </c>
       <c r="H16" s="22">
-        <f>MIN(9,MAX(1,COUNTIF($B$1:$B$10,"&gt;="&amp;D16)))</f>
+        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D16)*1)))</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1687,7 @@
         <v/>
       </c>
       <c r="H17" s="22">
-        <f>MIN(9,MAX(1,COUNTIF($B$1:$B$10,"&gt;="&amp;D17)))</f>
+        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D17)*1)))</f>
         <v/>
       </c>
     </row>

--- a/deg-concentration-calculator.xlsx
+++ b/deg-concentration-calculator.xlsx
@@ -7,7 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Расчёт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Лист1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Проверка" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Лист1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" calcMode="auto" fullCalcOnLoad="1"/>
@@ -16,13 +17,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="+0.0;-0.0;0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="PT Astra Serif"/>
       <charset val="204"/>
@@ -111,6 +113,12 @@
       <b val="1"/>
       <color rgb="00006400"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -253,7 +261,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
@@ -281,13 +289,13 @@
     <xf numFmtId="165" fontId="13" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="10" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -296,24 +304,45 @@
     <xf numFmtId="167" fontId="10" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="14" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="2" fontId="17" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="2" fontId="18" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -401,7 +430,7 @@
           <a:bodyPr/>
           <a:p>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
           </a:p>
         </rich>
@@ -433,7 +462,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="ru-RU"/>
         </a:p>
@@ -618,7 +647,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
@@ -683,7 +712,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
@@ -1037,13 +1066,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1063,7 +1092,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Метод: линейная интерполяция между двумя соседними точками таблицы (расчёт точно проходит через все табличные значения).</t>
+          <t>Метод: линейная интерполяция между двумя соседними точками таблицы. Проверка совпадения с таблицей — лист «Проверка».</t>
         </is>
       </c>
     </row>
@@ -1081,11 +1110,11 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>1.085</v>
+        <v>1.08634</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>← вводить только в эту жёлтую ячейку</t>
+          <t>← вводить только в эту жёлтую ячейку (лист «Расчёт»)</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1132,7 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>IF(NOT(ISNUMBER($B$6)),"Введите плотность (число)",IF(OR($B$6&lt;MIN('Лист1'!$B$1:$B$10),$B$6&gt;MAX('Лист1'!$B$1:$B$10)),"Вне диапазона таблицы",IFERROR(INDEX('Лист1'!$A$1:$A$10,$B$26)+(INDEX('Лист1'!$A$1:$A$10,$B$26+1)-INDEX('Лист1'!$A$1:$A$10,$B$26))*($B$6-INDEX('Лист1'!$B$1:$B$10,$B$26))/(INDEX('Лист1'!$B$1:$B$10,$B$26+1)-INDEX('Лист1'!$B$1:$B$10,$B$26)),"Ошибка расчёта")))</f>
+        <f>IF(NOT(ISNUMBER($B$6)),"Введите плотность (число)",IF(OR($B$6&lt;MIN('Лист1'!$B$1:$B$10),$B$6&gt;MAX('Лист1'!$B$1:$B$10)),"Вне диапазона таблицы",IFERROR(INDEX('Лист1'!$A$1:$A$10,$B$28)+(INDEX('Лист1'!$A$1:$A$10,$B$28+1)-INDEX('Лист1'!$A$1:$A$10,$B$28))*($B$6-INDEX('Лист1'!$B$1:$B$10,$B$28))/(INDEX('Лист1'!$B$1:$B$10,$B$28+1)-INDEX('Лист1'!$B$1:$B$10,$B$28)),"Ошибка расчёта")))</f>
         <v/>
       </c>
     </row>
@@ -1118,213 +1147,264 @@
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Диапазон применимости (по таблице), г/см³:</t>
-        </is>
-      </c>
-      <c r="B12" s="15">
-        <f>MIN('Лист1'!$B$1:$B$10)</f>
-        <v/>
-      </c>
-      <c r="C12" s="15">
-        <f>MAX('Лист1'!$B$1:$B$10)</f>
-        <v/>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>мин. … макс. (что соответствует 10 … 100 % масс.)</t>
-        </is>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Контрольный пересчёт вторым способом</t>
+        </is>
+      </c>
+      <c r="B11" s="15">
+        <f>IFERROR((INDEX('Лист1'!$A$1:$A$10,$B$29)*(INDEX('Лист1'!$B$1:$B$10,$B$29+1)-$B$6)+INDEX('Лист1'!$A$1:$A$10,$B$29+1)*($B$6-INDEX('Лист1'!$B$1:$B$10,$B$29)))/(INDEX('Лист1'!$B$1:$B$10,$B$29+1)-INDEX('Лист1'!$B$1:$B$10,$B$29)),"")</f>
+        <v/>
+      </c>
+      <c r="C11" s="9">
+        <f>IF(OR(NOT(ISNUMBER($B$9)),NOT(ISNUMBER($B$11))),"",IF(ABS($B$9-$B$11)&lt;0.0000001,"оба способа дают одно значение","РАСХОЖДЕНИЕ СПОСОБОВ — сообщите разработчику"))</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
+          <t>Диапазон применимости (по таблице), г/см³:</t>
+        </is>
+      </c>
+      <c r="B13" s="16">
+        <f>MIN('Лист1'!$B$1:$B$10)</f>
+        <v/>
+      </c>
+      <c r="C13" s="16">
+        <f>MAX('Лист1'!$B$1:$B$10)</f>
+        <v/>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>мин. … макс. (соответствует 10 … 100 % масс.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
           <t>Контроль исходной таблицы</t>
         </is>
       </c>
-      <c r="B13" s="11">
+      <c r="B14" s="11">
         <f>IF(AND(COUNT('Лист1'!$B$1:$B$10)=10,SUMPRODUCT(('Лист1'!$B$1:$B$9&lt;='Лист1'!$B$2:$B$10)*1)=0),"таблица в порядке: 10 точек, плотность убывает","ВНИМАНИЕ: таблица на листе «Лист1» изменена — проверьте A1:B10")</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>ИСПОЛЬЗОВАННЫЙ УЧАСТОК ТАБЛИЦЫ</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="16" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>нижняя точка</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>верхняя точка</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Плотность, г/см³</t>
         </is>
       </c>
-      <c r="B16" s="15">
-        <f>IF(ISNUMBER($B$26),INDEX('Лист1'!$B$1:$B$10,$B$26+1),"")</f>
-        <v/>
-      </c>
-      <c r="C16" s="15">
-        <f>IF(ISNUMBER($B$26),INDEX('Лист1'!$B$1:$B$10,$B$26+0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="B18" s="16">
+        <f>IF(ISNUMBER($B$28),INDEX('Лист1'!$B$1:$B$10,$B$28+1),"")</f>
+        <v/>
+      </c>
+      <c r="C18" s="16">
+        <f>IF(ISNUMBER($B$28),INDEX('Лист1'!$B$1:$B$10,$B$28+0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Концентрация, % масс.</t>
         </is>
       </c>
-      <c r="B17" s="17">
-        <f>IF(ISNUMBER($B$26),INDEX('Лист1'!$A$1:$A$10,$B$26+1),"")</f>
-        <v/>
-      </c>
-      <c r="C17" s="17">
-        <f>IF(ISNUMBER($B$26),INDEX('Лист1'!$A$1:$A$10,$B$26+0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>СПРАВОЧНО: расчёт по уравнению линейного тренда  C = a·ρ + b</t>
-        </is>
+      <c r="B19" s="15">
+        <f>IF(ISNUMBER($B$28),INDEX('Лист1'!$A$1:$A$10,$B$28+1),"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="15">
+        <f>IF(ISNUMBER($B$28),INDEX('Лист1'!$A$1:$A$10,$B$28+0),"")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>a (наклон)</t>
+          <t>Чувствительность на этом участке, % масс. на 0,001 г/см³</t>
         </is>
       </c>
       <c r="B20" s="18">
-        <f>SLOPE('Лист1'!$A$1:$A$10,'Лист1'!$B$1:$B$10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>b (отрезок)</t>
-        </is>
-      </c>
-      <c r="B21" s="18">
-        <f>INTERCEPT('Лист1'!$A$1:$A$10,'Лист1'!$B$1:$B$10)</f>
-        <v/>
+        <f>IFERROR(ABS((INDEX('Лист1'!$A$1:$A$10,$B$28+1)-INDEX('Лист1'!$A$1:$A$10,$B$28))/(INDEX('Лист1'!$B$1:$B$10,$B$28+1)-INDEX('Лист1'!$B$1:$B$10,$B$28)))*0.001,"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>на сколько сдвинется результат при ошибке плотности 0,001 г/см³</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>R²</t>
-        </is>
-      </c>
-      <c r="B22" s="19">
-        <f>RSQ('Лист1'!$A$1:$A$10,'Лист1'!$B$1:$B$10)</f>
-        <v/>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>СПРАВОЧНО: расчёт по уравнению линейного тренда  C = a·ρ + b</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>НЕ использовать как результат: зависимость нелинейна. Рабочий результат — ячейка B9.</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
+          <t>a (наклон)</t>
+        </is>
+      </c>
+      <c r="B23" s="18">
+        <f>SLOPE('Лист1'!$A$1:$A$10,'Лист1'!$B$1:$B$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>b (отрезок)</t>
+        </is>
+      </c>
+      <c r="B24" s="18">
+        <f>INTERCEPT('Лист1'!$A$1:$A$10,'Лист1'!$B$1:$B$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="B25" s="19">
+        <f>RSQ('Лист1'!$A$1:$A$10,'Лист1'!$B$1:$B$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
           <t>Концентрация по тренду, % масс.</t>
         </is>
       </c>
-      <c r="B23" s="17">
-        <f>IF(ISNUMBER($B$6),$B$20*$B$6+$B$21,"")</f>
-        <v/>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Только для сравнения: зависимость нелинейна, отклонение тренда от таблицы достигает ±10 % абс. В основном расчёте (ячейка B9) не используется.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="B26" s="15">
+        <f>IF(ISNUMBER($B$6),$B$23*$B$6+$B$24,"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>отклонение тренда от расчёта по таблице, % абс.:</t>
+        </is>
+      </c>
+      <c r="D26" s="20">
+        <f>IF(AND(ISNUMBER($B$9),ISNUMBER($B$26)),$B$26-$B$9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>Служебные ячейки (не изменять)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>Номер нижней точки интервала</t>
-        </is>
-      </c>
-      <c r="B26" s="21">
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Номер нижней точки интервала, способ 1</t>
+        </is>
+      </c>
+      <c r="B28" s="22">
         <f>IF(AND(ISNUMBER($B$6),$B$6&gt;=MIN('Лист1'!$B$1:$B$10),$B$6&lt;=MAX('Лист1'!$B$1:$B$10)),MIN(9,MAX(1,SUMPRODUCT(('Лист1'!$B$1:$B$10&gt;=$B$6)*1))),"")</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Номер нижней точки интервала, способ 2</t>
+        </is>
+      </c>
+      <c r="B29" s="22">
+        <f>IF(AND(ISNUMBER($B$6),$B$6&gt;=MIN('Лист1'!$B$1:$B$10),$B$6&lt;=MAX('Лист1'!$B$1:$B$10)),MIN(9,MAX(1,MATCH($B$6,'Лист1'!$B$1:$B$10,-1))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>ПОРЯДОК РАБОТЫ</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>1. Ввести измеренную плотность ДЭГ (г/см³) в жёлтую ячейку B6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>2. Концентрация ДЭГ в % масс. выводится в ячейке B9.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>3. Если введённая плотность выходит за пределы таблицы (B12…C12), выводится «Вне диапазона таблицы»: экстраполяция за пределы зависимости не выполняется.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>4. Плотность должна быть приведена к той же температуре, при которой получена исходная таблица (в исходных данных температура не указана — уточнить при необходимости).</t>
+          <t>1. Ввести измеренную плотность ДЭГ (г/см³) в жёлтую ячейку B6 этого листа.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>5. Исходную таблицу на листе «Лист1» (A1:B10) можно дополнять/править — расчёт использует её напрямую; значения плотности должны оставаться в порядке убывания.</t>
+          <t>2. Концентрация ДЭГ в % масс. выводится в ячейке B9. Ячейка B11 — тот же расчёт другой формулой, значения обязаны совпадать.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>6. Вводить плотность только в ячейку B6 ЭТОГО листа («Расчёт»). Не вводите её на листе «Лист1»: там в ячейках B1:B10 лежит сама зависимость, и ввод поверх них испортит таблицу.</t>
+          <t>3. Вне диапазона B13…C13 выводится «Вне диапазона таблицы»: экстраполяция не выполняется.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>7. Если результат не меняется при вводе новой плотности — в Excel включён ручной пересчёт: «Формулы» → «Параметры вычислений» → «Автоматически» (или нажмите F9).</t>
+          <t>4. Не вводить плотность на листе «Лист1»: в B1:B10 там лежит сама зависимость, ввод поверх неё испортит расчёт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>5. Если результат не меняется при вводе — включён ручной пересчёт: «Формулы» → «Параметры вычислений» → «Автоматически» (или F9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>6. Плотность должна быть приведена к температуре, при которой снята исходная таблица. Выше 50 % масс. зависимость очень пологая: ошибка плотности 0,001 г/см³ даёт до 2,6 % масс. по концентрации (см. лист «Проверка»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>7. Таблицу на «Лист1» можно дополнять точками — расчёт использует её напрямую; плотность должна оставаться в порядке убывания.</t>
         </is>
       </c>
     </row>
@@ -1339,377 +1419,810 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="3" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ПРОВЕРКА: расчёт в табличных точках обязан давать табличную концентрацию</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Каждая строка — точка исходной таблицы с листа «Лист1». Столбцы E и F — два независимых способа расчёта по той же зависимости.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Плотность из таблицы, г/см³</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Концентрация по таблице, % масс.</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>Расчёт, способ 1</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>Расчёт, способ 2</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>Отклонение от таблицы, % абс.</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>Расхождение способов, % абс.</t>
+        </is>
+      </c>
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t>служебн. k1</t>
+        </is>
+      </c>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>служебн. k2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="25">
+        <f>'Лист1'!B1</f>
+        <v/>
+      </c>
+      <c r="C5" s="26">
+        <f>'Лист1'!A1</f>
+        <v/>
+      </c>
+      <c r="E5" s="26">
+        <f>INDEX('Лист1'!$A$1:$A$10,$J5)+(INDEX('Лист1'!$A$1:$A$10,$J5+1)-INDEX('Лист1'!$A$1:$A$10,$J5))*($B5-INDEX('Лист1'!$B$1:$B$10,$J5))/(INDEX('Лист1'!$B$1:$B$10,$J5+1)-INDEX('Лист1'!$B$1:$B$10,$J5))</f>
+        <v/>
+      </c>
+      <c r="F5" s="26">
+        <f>(INDEX('Лист1'!$A$1:$A$10,$K5)*(INDEX('Лист1'!$B$1:$B$10,$K5+1)-$B5)+INDEX('Лист1'!$A$1:$A$10,$K5+1)*($B5-INDEX('Лист1'!$B$1:$B$10,$K5)))/(INDEX('Лист1'!$B$1:$B$10,$K5+1)-INDEX('Лист1'!$B$1:$B$10,$K5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="27">
+        <f>ABS(E5-C5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="27">
+        <f>ABS(E5-F5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="22">
+        <f>MIN(9,MAX(1,SUMPRODUCT(('Лист1'!$B$1:$B$10&gt;=$B5)*1)))</f>
+        <v/>
+      </c>
+      <c r="K5" s="22">
+        <f>MIN(9,MAX(1,MATCH($B5,'Лист1'!$B$1:$B$10,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="25">
+        <f>'Лист1'!B2</f>
+        <v/>
+      </c>
+      <c r="C6" s="26">
+        <f>'Лист1'!A2</f>
+        <v/>
+      </c>
+      <c r="E6" s="26">
+        <f>INDEX('Лист1'!$A$1:$A$10,$J6)+(INDEX('Лист1'!$A$1:$A$10,$J6+1)-INDEX('Лист1'!$A$1:$A$10,$J6))*($B6-INDEX('Лист1'!$B$1:$B$10,$J6))/(INDEX('Лист1'!$B$1:$B$10,$J6+1)-INDEX('Лист1'!$B$1:$B$10,$J6))</f>
+        <v/>
+      </c>
+      <c r="F6" s="26">
+        <f>(INDEX('Лист1'!$A$1:$A$10,$K6)*(INDEX('Лист1'!$B$1:$B$10,$K6+1)-$B6)+INDEX('Лист1'!$A$1:$A$10,$K6+1)*($B6-INDEX('Лист1'!$B$1:$B$10,$K6)))/(INDEX('Лист1'!$B$1:$B$10,$K6+1)-INDEX('Лист1'!$B$1:$B$10,$K6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="27">
+        <f>ABS(E6-C6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="27">
+        <f>ABS(E6-F6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="22">
+        <f>MIN(9,MAX(1,SUMPRODUCT(('Лист1'!$B$1:$B$10&gt;=$B6)*1)))</f>
+        <v/>
+      </c>
+      <c r="K6" s="22">
+        <f>MIN(9,MAX(1,MATCH($B6,'Лист1'!$B$1:$B$10,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="25">
+        <f>'Лист1'!B3</f>
+        <v/>
+      </c>
+      <c r="C7" s="26">
+        <f>'Лист1'!A3</f>
+        <v/>
+      </c>
+      <c r="E7" s="26">
+        <f>INDEX('Лист1'!$A$1:$A$10,$J7)+(INDEX('Лист1'!$A$1:$A$10,$J7+1)-INDEX('Лист1'!$A$1:$A$10,$J7))*($B7-INDEX('Лист1'!$B$1:$B$10,$J7))/(INDEX('Лист1'!$B$1:$B$10,$J7+1)-INDEX('Лист1'!$B$1:$B$10,$J7))</f>
+        <v/>
+      </c>
+      <c r="F7" s="26">
+        <f>(INDEX('Лист1'!$A$1:$A$10,$K7)*(INDEX('Лист1'!$B$1:$B$10,$K7+1)-$B7)+INDEX('Лист1'!$A$1:$A$10,$K7+1)*($B7-INDEX('Лист1'!$B$1:$B$10,$K7)))/(INDEX('Лист1'!$B$1:$B$10,$K7+1)-INDEX('Лист1'!$B$1:$B$10,$K7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="27">
+        <f>ABS(E7-C7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="27">
+        <f>ABS(E7-F7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="22">
+        <f>MIN(9,MAX(1,SUMPRODUCT(('Лист1'!$B$1:$B$10&gt;=$B7)*1)))</f>
+        <v/>
+      </c>
+      <c r="K7" s="22">
+        <f>MIN(9,MAX(1,MATCH($B7,'Лист1'!$B$1:$B$10,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="25">
+        <f>'Лист1'!B4</f>
+        <v/>
+      </c>
+      <c r="C8" s="26">
+        <f>'Лист1'!A4</f>
+        <v/>
+      </c>
+      <c r="E8" s="26">
+        <f>INDEX('Лист1'!$A$1:$A$10,$J8)+(INDEX('Лист1'!$A$1:$A$10,$J8+1)-INDEX('Лист1'!$A$1:$A$10,$J8))*($B8-INDEX('Лист1'!$B$1:$B$10,$J8))/(INDEX('Лист1'!$B$1:$B$10,$J8+1)-INDEX('Лист1'!$B$1:$B$10,$J8))</f>
+        <v/>
+      </c>
+      <c r="F8" s="26">
+        <f>(INDEX('Лист1'!$A$1:$A$10,$K8)*(INDEX('Лист1'!$B$1:$B$10,$K8+1)-$B8)+INDEX('Лист1'!$A$1:$A$10,$K8+1)*($B8-INDEX('Лист1'!$B$1:$B$10,$K8)))/(INDEX('Лист1'!$B$1:$B$10,$K8+1)-INDEX('Лист1'!$B$1:$B$10,$K8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="27">
+        <f>ABS(E8-C8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="27">
+        <f>ABS(E8-F8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="22">
+        <f>MIN(9,MAX(1,SUMPRODUCT(('Лист1'!$B$1:$B$10&gt;=$B8)*1)))</f>
+        <v/>
+      </c>
+      <c r="K8" s="22">
+        <f>MIN(9,MAX(1,MATCH($B8,'Лист1'!$B$1:$B$10,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="25">
+        <f>'Лист1'!B5</f>
+        <v/>
+      </c>
+      <c r="C9" s="26">
+        <f>'Лист1'!A5</f>
+        <v/>
+      </c>
+      <c r="E9" s="26">
+        <f>INDEX('Лист1'!$A$1:$A$10,$J9)+(INDEX('Лист1'!$A$1:$A$10,$J9+1)-INDEX('Лист1'!$A$1:$A$10,$J9))*($B9-INDEX('Лист1'!$B$1:$B$10,$J9))/(INDEX('Лист1'!$B$1:$B$10,$J9+1)-INDEX('Лист1'!$B$1:$B$10,$J9))</f>
+        <v/>
+      </c>
+      <c r="F9" s="26">
+        <f>(INDEX('Лист1'!$A$1:$A$10,$K9)*(INDEX('Лист1'!$B$1:$B$10,$K9+1)-$B9)+INDEX('Лист1'!$A$1:$A$10,$K9+1)*($B9-INDEX('Лист1'!$B$1:$B$10,$K9)))/(INDEX('Лист1'!$B$1:$B$10,$K9+1)-INDEX('Лист1'!$B$1:$B$10,$K9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="27">
+        <f>ABS(E9-C9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="27">
+        <f>ABS(E9-F9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="22">
+        <f>MIN(9,MAX(1,SUMPRODUCT(('Лист1'!$B$1:$B$10&gt;=$B9)*1)))</f>
+        <v/>
+      </c>
+      <c r="K9" s="22">
+        <f>MIN(9,MAX(1,MATCH($B9,'Лист1'!$B$1:$B$10,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="25">
+        <f>'Лист1'!B6</f>
+        <v/>
+      </c>
+      <c r="C10" s="26">
+        <f>'Лист1'!A6</f>
+        <v/>
+      </c>
+      <c r="E10" s="26">
+        <f>INDEX('Лист1'!$A$1:$A$10,$J10)+(INDEX('Лист1'!$A$1:$A$10,$J10+1)-INDEX('Лист1'!$A$1:$A$10,$J10))*($B10-INDEX('Лист1'!$B$1:$B$10,$J10))/(INDEX('Лист1'!$B$1:$B$10,$J10+1)-INDEX('Лист1'!$B$1:$B$10,$J10))</f>
+        <v/>
+      </c>
+      <c r="F10" s="26">
+        <f>(INDEX('Лист1'!$A$1:$A$10,$K10)*(INDEX('Лист1'!$B$1:$B$10,$K10+1)-$B10)+INDEX('Лист1'!$A$1:$A$10,$K10+1)*($B10-INDEX('Лист1'!$B$1:$B$10,$K10)))/(INDEX('Лист1'!$B$1:$B$10,$K10+1)-INDEX('Лист1'!$B$1:$B$10,$K10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="27">
+        <f>ABS(E10-C10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="27">
+        <f>ABS(E10-F10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="22">
+        <f>MIN(9,MAX(1,SUMPRODUCT(('Лист1'!$B$1:$B$10&gt;=$B10)*1)))</f>
+        <v/>
+      </c>
+      <c r="K10" s="22">
+        <f>MIN(9,MAX(1,MATCH($B10,'Лист1'!$B$1:$B$10,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="25">
+        <f>'Лист1'!B7</f>
+        <v/>
+      </c>
+      <c r="C11" s="26">
+        <f>'Лист1'!A7</f>
+        <v/>
+      </c>
+      <c r="E11" s="26">
+        <f>INDEX('Лист1'!$A$1:$A$10,$J11)+(INDEX('Лист1'!$A$1:$A$10,$J11+1)-INDEX('Лист1'!$A$1:$A$10,$J11))*($B11-INDEX('Лист1'!$B$1:$B$10,$J11))/(INDEX('Лист1'!$B$1:$B$10,$J11+1)-INDEX('Лист1'!$B$1:$B$10,$J11))</f>
+        <v/>
+      </c>
+      <c r="F11" s="26">
+        <f>(INDEX('Лист1'!$A$1:$A$10,$K11)*(INDEX('Лист1'!$B$1:$B$10,$K11+1)-$B11)+INDEX('Лист1'!$A$1:$A$10,$K11+1)*($B11-INDEX('Лист1'!$B$1:$B$10,$K11)))/(INDEX('Лист1'!$B$1:$B$10,$K11+1)-INDEX('Лист1'!$B$1:$B$10,$K11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="27">
+        <f>ABS(E11-C11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="27">
+        <f>ABS(E11-F11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="22">
+        <f>MIN(9,MAX(1,SUMPRODUCT(('Лист1'!$B$1:$B$10&gt;=$B11)*1)))</f>
+        <v/>
+      </c>
+      <c r="K11" s="22">
+        <f>MIN(9,MAX(1,MATCH($B11,'Лист1'!$B$1:$B$10,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="25">
+        <f>'Лист1'!B8</f>
+        <v/>
+      </c>
+      <c r="C12" s="26">
+        <f>'Лист1'!A8</f>
+        <v/>
+      </c>
+      <c r="E12" s="26">
+        <f>INDEX('Лист1'!$A$1:$A$10,$J12)+(INDEX('Лист1'!$A$1:$A$10,$J12+1)-INDEX('Лист1'!$A$1:$A$10,$J12))*($B12-INDEX('Лист1'!$B$1:$B$10,$J12))/(INDEX('Лист1'!$B$1:$B$10,$J12+1)-INDEX('Лист1'!$B$1:$B$10,$J12))</f>
+        <v/>
+      </c>
+      <c r="F12" s="26">
+        <f>(INDEX('Лист1'!$A$1:$A$10,$K12)*(INDEX('Лист1'!$B$1:$B$10,$K12+1)-$B12)+INDEX('Лист1'!$A$1:$A$10,$K12+1)*($B12-INDEX('Лист1'!$B$1:$B$10,$K12)))/(INDEX('Лист1'!$B$1:$B$10,$K12+1)-INDEX('Лист1'!$B$1:$B$10,$K12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="27">
+        <f>ABS(E12-C12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="27">
+        <f>ABS(E12-F12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="22">
+        <f>MIN(9,MAX(1,SUMPRODUCT(('Лист1'!$B$1:$B$10&gt;=$B12)*1)))</f>
+        <v/>
+      </c>
+      <c r="K12" s="22">
+        <f>MIN(9,MAX(1,MATCH($B12,'Лист1'!$B$1:$B$10,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="25">
+        <f>'Лист1'!B9</f>
+        <v/>
+      </c>
+      <c r="C13" s="26">
+        <f>'Лист1'!A9</f>
+        <v/>
+      </c>
+      <c r="E13" s="26">
+        <f>INDEX('Лист1'!$A$1:$A$10,$J13)+(INDEX('Лист1'!$A$1:$A$10,$J13+1)-INDEX('Лист1'!$A$1:$A$10,$J13))*($B13-INDEX('Лист1'!$B$1:$B$10,$J13))/(INDEX('Лист1'!$B$1:$B$10,$J13+1)-INDEX('Лист1'!$B$1:$B$10,$J13))</f>
+        <v/>
+      </c>
+      <c r="F13" s="26">
+        <f>(INDEX('Лист1'!$A$1:$A$10,$K13)*(INDEX('Лист1'!$B$1:$B$10,$K13+1)-$B13)+INDEX('Лист1'!$A$1:$A$10,$K13+1)*($B13-INDEX('Лист1'!$B$1:$B$10,$K13)))/(INDEX('Лист1'!$B$1:$B$10,$K13+1)-INDEX('Лист1'!$B$1:$B$10,$K13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="27">
+        <f>ABS(E13-C13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="27">
+        <f>ABS(E13-F13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="22">
+        <f>MIN(9,MAX(1,SUMPRODUCT(('Лист1'!$B$1:$B$10&gt;=$B13)*1)))</f>
+        <v/>
+      </c>
+      <c r="K13" s="22">
+        <f>MIN(9,MAX(1,MATCH($B13,'Лист1'!$B$1:$B$10,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="25">
+        <f>'Лист1'!B10</f>
+        <v/>
+      </c>
+      <c r="C14" s="26">
+        <f>'Лист1'!A10</f>
+        <v/>
+      </c>
+      <c r="E14" s="26">
+        <f>INDEX('Лист1'!$A$1:$A$10,$J14)+(INDEX('Лист1'!$A$1:$A$10,$J14+1)-INDEX('Лист1'!$A$1:$A$10,$J14))*($B14-INDEX('Лист1'!$B$1:$B$10,$J14))/(INDEX('Лист1'!$B$1:$B$10,$J14+1)-INDEX('Лист1'!$B$1:$B$10,$J14))</f>
+        <v/>
+      </c>
+      <c r="F14" s="26">
+        <f>(INDEX('Лист1'!$A$1:$A$10,$K14)*(INDEX('Лист1'!$B$1:$B$10,$K14+1)-$B14)+INDEX('Лист1'!$A$1:$A$10,$K14+1)*($B14-INDEX('Лист1'!$B$1:$B$10,$K14)))/(INDEX('Лист1'!$B$1:$B$10,$K14+1)-INDEX('Лист1'!$B$1:$B$10,$K14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="27">
+        <f>ABS(E14-C14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="27">
+        <f>ABS(E14-F14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="22">
+        <f>MIN(9,MAX(1,SUMPRODUCT(('Лист1'!$B$1:$B$10&gt;=$B14)*1)))</f>
+        <v/>
+      </c>
+      <c r="K14" s="22">
+        <f>MIN(9,MAX(1,MATCH($B14,'Лист1'!$B$1:$B$10,-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Максимальное отклонение, % абс.:</t>
+        </is>
+      </c>
+      <c r="G16" s="28">
+        <f>MAX(G5:G14)</f>
+        <v/>
+      </c>
+      <c r="H16" s="28">
+        <f>MAX(H5:H14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="11">
+        <f>IF(MAX(G5:G14)&lt;0.0000001,"Проверка пройдена: расчёт точно воспроизводит все 10 точек таблицы","ПРОВЕРКА НЕ ПРОЙДЕНА — таблица изменена или нарушен порядок убывания плотности")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>ЧУВСТВИТЕЛЬНОСТЬ РАСЧЁТА ПО УЧАСТКАМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Чем выше концентрация, тем меньше изменение плотности на 10 % масс. — тем сильнее результат зависит от точности измерения плотности и от температуры, к которой приведена плотность.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Участок, % масс.</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>Δρ на участке, г/см³</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>Крутизна dC/dρ, % на 1 г/см³</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>Сдвиг результата при ошибке ρ 0,001 г/см³, % масс.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29">
+        <f>'Лист1'!A2&amp;" – "&amp;'Лист1'!A1</f>
+        <v/>
+      </c>
+      <c r="C22" s="25">
+        <f>'Лист1'!B1-'Лист1'!B2</f>
+        <v/>
+      </c>
+      <c r="E22" s="24">
+        <f>('Лист1'!A1-'Лист1'!A2)/('Лист1'!B1-'Лист1'!B2)</f>
+        <v/>
+      </c>
+      <c r="G22" s="30">
+        <f>E22*0.001</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29">
+        <f>'Лист1'!A3&amp;" – "&amp;'Лист1'!A2</f>
+        <v/>
+      </c>
+      <c r="C23" s="25">
+        <f>'Лист1'!B2-'Лист1'!B3</f>
+        <v/>
+      </c>
+      <c r="E23" s="24">
+        <f>('Лист1'!A2-'Лист1'!A3)/('Лист1'!B2-'Лист1'!B3)</f>
+        <v/>
+      </c>
+      <c r="G23" s="30">
+        <f>E23*0.001</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29">
+        <f>'Лист1'!A4&amp;" – "&amp;'Лист1'!A3</f>
+        <v/>
+      </c>
+      <c r="C24" s="25">
+        <f>'Лист1'!B3-'Лист1'!B4</f>
+        <v/>
+      </c>
+      <c r="E24" s="24">
+        <f>('Лист1'!A3-'Лист1'!A4)/('Лист1'!B3-'Лист1'!B4)</f>
+        <v/>
+      </c>
+      <c r="G24" s="30">
+        <f>E24*0.001</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29">
+        <f>'Лист1'!A5&amp;" – "&amp;'Лист1'!A4</f>
+        <v/>
+      </c>
+      <c r="C25" s="25">
+        <f>'Лист1'!B4-'Лист1'!B5</f>
+        <v/>
+      </c>
+      <c r="E25" s="24">
+        <f>('Лист1'!A4-'Лист1'!A5)/('Лист1'!B4-'Лист1'!B5)</f>
+        <v/>
+      </c>
+      <c r="G25" s="30">
+        <f>E25*0.001</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29">
+        <f>'Лист1'!A6&amp;" – "&amp;'Лист1'!A5</f>
+        <v/>
+      </c>
+      <c r="C26" s="25">
+        <f>'Лист1'!B5-'Лист1'!B6</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
+        <f>('Лист1'!A5-'Лист1'!A6)/('Лист1'!B5-'Лист1'!B6)</f>
+        <v/>
+      </c>
+      <c r="G26" s="30">
+        <f>E26*0.001</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29">
+        <f>'Лист1'!A7&amp;" – "&amp;'Лист1'!A6</f>
+        <v/>
+      </c>
+      <c r="C27" s="25">
+        <f>'Лист1'!B6-'Лист1'!B7</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
+        <f>('Лист1'!A6-'Лист1'!A7)/('Лист1'!B6-'Лист1'!B7)</f>
+        <v/>
+      </c>
+      <c r="G27" s="30">
+        <f>E27*0.001</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="29">
+        <f>'Лист1'!A8&amp;" – "&amp;'Лист1'!A7</f>
+        <v/>
+      </c>
+      <c r="C28" s="25">
+        <f>'Лист1'!B7-'Лист1'!B8</f>
+        <v/>
+      </c>
+      <c r="E28" s="24">
+        <f>('Лист1'!A7-'Лист1'!A8)/('Лист1'!B7-'Лист1'!B8)</f>
+        <v/>
+      </c>
+      <c r="G28" s="30">
+        <f>E28*0.001</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="29">
+        <f>'Лист1'!A9&amp;" – "&amp;'Лист1'!A8</f>
+        <v/>
+      </c>
+      <c r="C29" s="25">
+        <f>'Лист1'!B8-'Лист1'!B9</f>
+        <v/>
+      </c>
+      <c r="E29" s="24">
+        <f>('Лист1'!A8-'Лист1'!A9)/('Лист1'!B8-'Лист1'!B9)</f>
+        <v/>
+      </c>
+      <c r="G29" s="30">
+        <f>E29*0.001</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="29">
+        <f>'Лист1'!A10&amp;" – "&amp;'Лист1'!A9</f>
+        <v/>
+      </c>
+      <c r="C30" s="25">
+        <f>'Лист1'!B9-'Лист1'!B10</f>
+        <v/>
+      </c>
+      <c r="E30" s="24">
+        <f>('Лист1'!A9-'Лист1'!A10)/('Лист1'!B9-'Лист1'!B10)</f>
+        <v/>
+      </c>
+      <c r="G30" s="30">
+        <f>E30*0.001</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.875" customWidth="1" min="1" max="1"/>
     <col width="10.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="n">
+      <c r="A1" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="B1" s="22" t="n">
+      <c r="B1" s="31" t="n">
         <v>1.116</v>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>Исходная зависимость (не изменять структуру):</t>
-        </is>
-      </c>
-      <c r="F1" s="22" t="n"/>
+          <t>Исходная зависимость. Столбец A — концентрация ДЭГ, % масс., столбец B — плотность ДЭГ, г/см³.</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="n">
+      <c r="A2" s="31" t="n">
         <v>90</v>
       </c>
-      <c r="B2" s="22" t="n">
+      <c r="B2" s="31" t="n">
         <v>1.1121</v>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>столбец A — концентрация ДЭГ, % масс.</t>
+          <t>Плотность должна оставаться в порядке убывания. Ввод измеренной плотности выполняется на листе «Расчёт», ячейка B6, а не здесь.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="n">
+      <c r="A3" s="31" t="n">
         <v>80</v>
       </c>
-      <c r="B3" s="22" t="n">
+      <c r="B3" s="31" t="n">
         <v>1.10577</v>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>столбец B — плотность ДЭГ, г/см³</t>
+          <t>Проверка совпадения расчёта с этой таблицей — на листе «Проверка».</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="n">
+      <c r="A4" s="31" t="n">
         <v>70</v>
       </c>
-      <c r="B4" s="22" t="n">
+      <c r="B4" s="31" t="n">
         <v>1.09759</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="n">
+      <c r="A5" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="31" t="n">
         <v>1.08634</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="31" t="n">
         <v>1.07287</v>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>ПРОВЕРКА МЕТОДА: расчёт по табличным значениям плотности должен вернуть табличную концентрацию</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="n">
+      <c r="A7" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="31" t="n">
         <v>1.0593</v>
       </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>Плотность, г/см³</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>Расчёт, % масс.</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>Таблица, % масс.</t>
-        </is>
-      </c>
-      <c r="G7" s="23" t="inlineStr">
-        <is>
-          <t>Отклонение |расчёт − таблица|, % абс.</t>
-        </is>
-      </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>служебн. k</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="31" t="n">
         <v>1.04376</v>
       </c>
-      <c r="D8" s="24">
-        <f>B1</f>
-        <v/>
-      </c>
-      <c r="E8" s="25">
-        <f>INDEX($A$1:$A$10,H8)+(INDEX($A$1:$A$10,H8+1)-INDEX($A$1:$A$10,H8))*(D8-INDEX($B$1:$B$10,H8))/(INDEX($B$1:$B$10,H8+1)-INDEX($B$1:$B$10,H8))</f>
-        <v/>
-      </c>
-      <c r="F8" s="25">
-        <f>A1</f>
-        <v/>
-      </c>
-      <c r="G8" s="26">
-        <f>ABS(E8-F8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="22">
-        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D8)*1)))</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="31" t="n">
         <v>1.02941</v>
       </c>
-      <c r="D9" s="24">
-        <f>B2</f>
-        <v/>
-      </c>
-      <c r="E9" s="25">
-        <f>INDEX($A$1:$A$10,H9)+(INDEX($A$1:$A$10,H9+1)-INDEX($A$1:$A$10,H9))*(D9-INDEX($B$1:$B$10,H9))/(INDEX($B$1:$B$10,H9+1)-INDEX($B$1:$B$10,H9))</f>
-        <v/>
-      </c>
-      <c r="F9" s="25">
-        <f>A2</f>
-        <v/>
-      </c>
-      <c r="G9" s="26">
-        <f>ABS(E9-F9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="22">
-        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D9)*1)))</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="31" t="n">
         <v>1.01322</v>
       </c>
-      <c r="D10" s="24">
-        <f>B3</f>
-        <v/>
-      </c>
-      <c r="E10" s="25">
-        <f>INDEX($A$1:$A$10,H10)+(INDEX($A$1:$A$10,H10+1)-INDEX($A$1:$A$10,H10))*(D10-INDEX($B$1:$B$10,H10))/(INDEX($B$1:$B$10,H10+1)-INDEX($B$1:$B$10,H10))</f>
-        <v/>
-      </c>
-      <c r="F10" s="25">
-        <f>A3</f>
-        <v/>
-      </c>
-      <c r="G10" s="26">
-        <f>ABS(E10-F10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="22">
-        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D10)*1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="D11" s="24">
-        <f>B4</f>
-        <v/>
-      </c>
-      <c r="E11" s="25">
-        <f>INDEX($A$1:$A$10,H11)+(INDEX($A$1:$A$10,H11+1)-INDEX($A$1:$A$10,H11))*(D11-INDEX($B$1:$B$10,H11))/(INDEX($B$1:$B$10,H11+1)-INDEX($B$1:$B$10,H11))</f>
-        <v/>
-      </c>
-      <c r="F11" s="25">
-        <f>A4</f>
-        <v/>
-      </c>
-      <c r="G11" s="26">
-        <f>ABS(E11-F11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="22">
-        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D11)*1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="D12" s="24">
-        <f>B5</f>
-        <v/>
-      </c>
-      <c r="E12" s="25">
-        <f>INDEX($A$1:$A$10,H12)+(INDEX($A$1:$A$10,H12+1)-INDEX($A$1:$A$10,H12))*(D12-INDEX($B$1:$B$10,H12))/(INDEX($B$1:$B$10,H12+1)-INDEX($B$1:$B$10,H12))</f>
-        <v/>
-      </c>
-      <c r="F12" s="25">
-        <f>A5</f>
-        <v/>
-      </c>
-      <c r="G12" s="26">
-        <f>ABS(E12-F12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="22">
-        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D12)*1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="D13" s="24">
-        <f>B6</f>
-        <v/>
-      </c>
-      <c r="E13" s="25">
-        <f>INDEX($A$1:$A$10,H13)+(INDEX($A$1:$A$10,H13+1)-INDEX($A$1:$A$10,H13))*(D13-INDEX($B$1:$B$10,H13))/(INDEX($B$1:$B$10,H13+1)-INDEX($B$1:$B$10,H13))</f>
-        <v/>
-      </c>
-      <c r="F13" s="25">
-        <f>A6</f>
-        <v/>
-      </c>
-      <c r="G13" s="26">
-        <f>ABS(E13-F13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="22">
-        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D13)*1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="D14" s="24">
-        <f>B7</f>
-        <v/>
-      </c>
-      <c r="E14" s="25">
-        <f>INDEX($A$1:$A$10,H14)+(INDEX($A$1:$A$10,H14+1)-INDEX($A$1:$A$10,H14))*(D14-INDEX($B$1:$B$10,H14))/(INDEX($B$1:$B$10,H14+1)-INDEX($B$1:$B$10,H14))</f>
-        <v/>
-      </c>
-      <c r="F14" s="25">
-        <f>A7</f>
-        <v/>
-      </c>
-      <c r="G14" s="26">
-        <f>ABS(E14-F14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="22">
-        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D14)*1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="D15" s="24">
-        <f>B8</f>
-        <v/>
-      </c>
-      <c r="E15" s="25">
-        <f>INDEX($A$1:$A$10,H15)+(INDEX($A$1:$A$10,H15+1)-INDEX($A$1:$A$10,H15))*(D15-INDEX($B$1:$B$10,H15))/(INDEX($B$1:$B$10,H15+1)-INDEX($B$1:$B$10,H15))</f>
-        <v/>
-      </c>
-      <c r="F15" s="25">
-        <f>A8</f>
-        <v/>
-      </c>
-      <c r="G15" s="26">
-        <f>ABS(E15-F15)</f>
-        <v/>
-      </c>
-      <c r="H15" s="22">
-        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D15)*1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="D16" s="24">
-        <f>B9</f>
-        <v/>
-      </c>
-      <c r="E16" s="25">
-        <f>INDEX($A$1:$A$10,H16)+(INDEX($A$1:$A$10,H16+1)-INDEX($A$1:$A$10,H16))*(D16-INDEX($B$1:$B$10,H16))/(INDEX($B$1:$B$10,H16+1)-INDEX($B$1:$B$10,H16))</f>
-        <v/>
-      </c>
-      <c r="F16" s="25">
-        <f>A9</f>
-        <v/>
-      </c>
-      <c r="G16" s="26">
-        <f>ABS(E16-F16)</f>
-        <v/>
-      </c>
-      <c r="H16" s="22">
-        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D16)*1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="D17" s="24">
-        <f>B10</f>
-        <v/>
-      </c>
-      <c r="E17" s="25">
-        <f>INDEX($A$1:$A$10,H17)+(INDEX($A$1:$A$10,H17+1)-INDEX($A$1:$A$10,H17))*(D17-INDEX($B$1:$B$10,H17))/(INDEX($B$1:$B$10,H17+1)-INDEX($B$1:$B$10,H17))</f>
-        <v/>
-      </c>
-      <c r="F17" s="25">
-        <f>A10</f>
-        <v/>
-      </c>
-      <c r="G17" s="26">
-        <f>ABS(E17-F17)</f>
-        <v/>
-      </c>
-      <c r="H17" s="22">
-        <f>MIN(9,MAX(1,SUMPRODUCT(($B$1:$B$10&gt;=D17)*1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Максимальное отклонение расчёта от таблицы, % абс.:</t>
-        </is>
-      </c>
-      <c r="G19" s="26">
-        <f>MAX(G8:G17)</f>
-        <v/>
-      </c>
-    </row>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>Коэфициенты из уравнения тренда (справочно, в расчёте не используются)</t>
         </is>
       </c>
-      <c r="B28" s="28" t="n"/>
-      <c r="C28" s="28" t="n"/>
+      <c r="B28" s="33" t="n"/>
+      <c r="C28" s="33" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1729,19 +2242,21 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A30" s="29">
+      <c r="A30" s="34">
         <f>SLOPE(A1:A10,B1:B10)</f>
         <v/>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="35">
         <f>INTERCEPT(A1:A10,B1:B10)</f>
         <v/>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="36">
         <f>CORREL(A1:A10,B1:B10)^2</f>
         <v/>
       </c>
     </row>
+    <row r="31"/>
+    <row r="32"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A28:C28"/>

--- a/deg-concentration-calculator.xlsx
+++ b/deg-concentration-calculator.xlsx
@@ -261,7 +261,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
@@ -282,8 +282,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="13" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -336,6 +337,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
@@ -422,34 +424,35 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <layout/>
-      <overlay val="0"/>
-      <spPr>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
-          <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-      <txPr>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -461,34 +464,32 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
           <a:endParaRPr lang="ru-RU"/>
         </a:p>
-      </txPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <scatterChart>
-        <scatterStyle val="smoothMarker"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
-            <spPr>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -496,110 +497,115 @@
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
-                <a:prstDash val="solid"/>
               </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>Лист1!$A$1:$A$10</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>100</v>
-                </pt>
-                <pt idx="1">
-                  <v>90</v>
-                </pt>
-                <pt idx="2">
-                  <v>80</v>
-                </pt>
-                <pt idx="3">
-                  <v>70</v>
-                </pt>
-                <pt idx="4">
-                  <v>60</v>
-                </pt>
-                <pt idx="5">
-                  <v>50</v>
-                </pt>
-                <pt idx="6">
-                  <v>40</v>
-                </pt>
-                <pt idx="7">
-                  <v>30</v>
-                </pt>
-                <pt idx="8">
-                  <v>20</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>Лист1!$B$1:$B$10</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="10"/>
-                <pt idx="0">
-                  <v>1.116</v>
-                </pt>
-                <pt idx="1">
-                  <v>1.1121</v>
-                </pt>
-                <pt idx="2">
-                  <v>1.10577</v>
-                </pt>
-                <pt idx="3">
-                  <v>1.09759</v>
-                </pt>
-                <pt idx="4">
-                  <v>1.08634</v>
-                </pt>
-                <pt idx="5">
-                  <v>1.07287</v>
-                </pt>
-                <pt idx="6">
-                  <v>1.0593</v>
-                </pt>
-                <pt idx="7">
-                  <v>1.04376</v>
-                </pt>
-                <pt idx="8">
-                  <v>1.02941</v>
-                </pt>
-                <pt idx="9">
-                  <v>1.01322</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </yVal>
-          <smooth val="1"/>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <axId val="593799039"/>
-        <axId val="593802367"/>
-      </scatterChart>
-      <valAx>
-        <axId val="593799039"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <majorGridlines>
-          <spPr>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$A$1:$A$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$B$1:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.1160000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1121000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1057699999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0975900000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0863400000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.07287</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0592999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.04376</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.0294099999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.01322</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AE2A-4580-AAB6-D1C7B085D57E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="593799039"/>
+        <c:axId val="593802367"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="593799039"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
@@ -607,16 +613,16 @@
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
@@ -625,16 +631,16 @@
                 <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:prstDash val="solid"/>
             <a:round/>
           </a:ln>
-        </spPr>
-        <txPr>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -646,25 +652,22 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
-        </txPr>
-        <crossAx val="593802367"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="midCat"/>
-      </valAx>
-      <valAx>
-        <axId val="593802367"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
+        </c:txPr>
+        <c:crossAx val="593802367"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="593802367"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
@@ -672,16 +675,16 @@
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
@@ -690,16 +693,16 @@
                 <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:prstDash val="solid"/>
             <a:round/>
           </a:ln>
-        </spPr>
-        <txPr>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -711,21 +714,26 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
-        </txPr>
-        <crossAx val="593799039"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="midCat"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
+        </c:txPr>
+        <c:crossAx val="593799039"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
     <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
@@ -736,11 +744,582 @@
           <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:prstDash val="solid"/>
       <a:round/>
     </a:ln>
-  </spPr>
-</chartSpace>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1066,7 +1645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1096,6 +1675,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1110,7 +1690,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>1.08634</v>
+        <v>1.08</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
@@ -1118,6 +1698,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
@@ -1162,6 +1743,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -1193,6 +1775,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
@@ -1258,6 +1841,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -1352,6 +1936,7 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
@@ -1408,7 +1993,10 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2095,12 +2683,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.875" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="10.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2110,11 +2697,6 @@
       <c r="B1" s="31" t="n">
         <v>1.116</v>
       </c>
-      <c r="D1" s="9" t="inlineStr">
-        <is>
-          <t>Исходная зависимость. Столбец A — концентрация ДЭГ, % масс., столбец B — плотность ДЭГ, г/см³.</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="31" t="n">
@@ -2123,11 +2705,6 @@
       <c r="B2" s="31" t="n">
         <v>1.1121</v>
       </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>Плотность должна оставаться в порядке убывания. Ввод измеренной плотности выполняется на листе «Расчёт», ячейка B6, а не здесь.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="31" t="n">
@@ -2135,11 +2712,6 @@
       </c>
       <c r="B3" s="31" t="n">
         <v>1.10577</v>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Проверка совпадения расчёта с этой таблицей — на листе «Проверка».</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -2204,10 +2776,33 @@
     <row r="14"/>
     <row r="15"/>
     <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>ИСХОДНАЯ ЗАВИСИМОСТЬ (A1:B10): столбец A — концентрация ДЭГ, % масс., столбец B — плотность ДЭГ, г/см³.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Лист защищён от изменений: ввод измеренной плотности выполняется на листе «Расчёт» в ячейке B6, а не здесь. Чтобы править саму зависимость: «Рецензирование» → «Снять защиту листа» (пароль не задан).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32">
+        <f>IF(AND(COUNT($B$1:$B$10)=10,SUMPRODUCT(($B$1:$B$9&lt;=$B$2:$B$10)*1)=0),"Таблица цела: 10 точек, плотность строго убывает.","ВНИМАНИЕ: таблица повреждена — есть одинаковые или неубывающие значения плотности. Проверьте B1:B10, восстановите исходные значения (60 % = 1,08634; 50 % = 1,07287).")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Проверка совпадения расчёта с этой таблицей — на листе «Проверка».</t>
+        </is>
+      </c>
+    </row>
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
@@ -2216,13 +2811,13 @@
     <row r="26"/>
     <row r="27"/>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A28" s="32" t="inlineStr">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>Коэфициенты из уравнения тренда (справочно, в расчёте не используются)</t>
         </is>
       </c>
-      <c r="B28" s="33" t="n"/>
-      <c r="C28" s="33" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="34" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2242,22 +2837,30 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A30" s="34">
+      <c r="A30" s="35">
         <f>SLOPE(A1:A10,B1:B10)</f>
         <v/>
       </c>
-      <c r="B30" s="35">
+      <c r="B30" s="36">
         <f>INTERCEPT(A1:A10,B1:B10)</f>
         <v/>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="37">
         <f>CORREL(A1:A10,B1:B10)^2</f>
         <v/>
       </c>
     </row>
     <row r="31"/>
     <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A28:C28"/>
   </mergeCells>

--- a/deg-concentration-calculator.xlsx
+++ b/deg-concentration-calculator.xlsx
@@ -282,9 +282,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="13" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1645,7 +1644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1675,7 +1674,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1698,7 +1696,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
@@ -1743,7 +1740,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -1775,7 +1771,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
@@ -1841,7 +1836,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -1936,7 +1930,6 @@
         <v/>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
@@ -1947,7 +1940,7 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>1. Ввести измеренную плотность ДЭГ (г/см³) в жёлтую ячейку B6 этого листа.</t>
+          <t>1. Ввести измеренную плотность ДЭГ (г/см³) в жёлтую ячейку B6 этого листа. Лист «Расчёт» не защищён, ввод свободный.</t>
         </is>
       </c>
     </row>
@@ -1993,10 +1986,7 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
